--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.71755107724452</v>
+        <v>10.02910205005223</v>
       </c>
       <c r="D2" t="n">
-        <v>61.65700370106008</v>
+        <v>10.01926310142226</v>
       </c>
       <c r="E2" t="n">
-        <v>14.67716204713844</v>
+        <v>2.385038832659995</v>
       </c>
       <c r="F2" t="n">
-        <v>15.54094318460882</v>
+        <v>2.525403267498934</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.10045138461668</v>
+        <v>9.116323350000211</v>
       </c>
       <c r="D3" t="n">
-        <v>56.04895061906159</v>
+        <v>9.107954475597507</v>
       </c>
       <c r="E3" t="n">
-        <v>14.67716204713844</v>
+        <v>2.385038832659995</v>
       </c>
       <c r="F3" t="n">
-        <v>15.54094318460882</v>
+        <v>2.525403267498934</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.1564073697108</v>
+        <v>4.575416197578004</v>
       </c>
       <c r="D4" t="n">
-        <v>26.24536419506917</v>
+        <v>4.26487168169874</v>
       </c>
       <c r="E4" t="n">
-        <v>14.67716204713844</v>
+        <v>2.385038832659995</v>
       </c>
       <c r="F4" t="n">
-        <v>15.54094318460882</v>
+        <v>2.525403267498934</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
